--- a/data/trans_dic/P80_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P80_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,21</t>
+          <t>1,57; 8,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 7,15</t>
+          <t>1,72; 6,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,97</t>
+          <t>2,15; 6,17</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,56</t>
+          <t>2,2; 7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,41</t>
+          <t>0,78; 3,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,19</t>
+          <t>1,74; 4,4</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,0</t>
+          <t>1,82; 4,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,81</t>
+          <t>0,99; 2,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,37</t>
+          <t>1,66; 3,45</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,83</t>
+          <t>1,41; 3,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,34</t>
+          <t>1,15; 2,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,21</t>
+          <t>1,48; 2,87</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,08</t>
+          <t>0,43; 1,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,88</t>
+          <t>0,51; 1,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,63</t>
+          <t>0,6; 1,6</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,26</t>
+          <t>0,12; 1,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,94</t>
+          <t>0,22; 1,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,83</t>
+          <t>0,25; 1,06</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,51</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,56</t>
+          <t>1,72; 2,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,73</t>
+          <t>1,17; 1,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,98</t>
+          <t>1,52; 2,27</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>16013</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11987</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>29042</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3360; 28858</t>
+          <t>6401; 34176</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5746; 22381</t>
+          <t>6230; 25224</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11833; 42603</t>
+          <t>16549; 47559</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>19354</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8292</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23769</t>
+          <t>27793</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7877; 27796</t>
+          <t>10507; 33462</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3374; 17416</t>
+          <t>3886; 15681</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14281; 39113</t>
+          <t>17045; 42942</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16864</t>
+          <t>19232</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>29959</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9684; 26816</t>
+          <t>11279; 30559</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4954; 15256</t>
+          <t>6190; 17293</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17276; 36409</t>
+          <t>20656; 42842</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>10668</t>
+          <t>13081</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24157</t>
+          <t>29447</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5138; 25071</t>
+          <t>9829; 25476</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6591; 16616</t>
+          <t>8454; 20530</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13443; 35289</t>
+          <t>21174; 41071</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>12305</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2456; 11679</t>
+          <t>2611; 12124</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2573; 10285</t>
+          <t>3086; 11769</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6386; 18060</t>
+          <t>7303; 19475</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2715</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4474</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>514; 4633</t>
+          <t>502; 5088</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>383; 5724</t>
+          <t>977; 6234</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1324; 8067</t>
+          <t>2089; 8925</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1178</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4261</t>
+          <t>0; 3984</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3622</t>
+          <t>0; 4160</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>44958; 88555</t>
+          <t>60769; 104966</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36004; 63275</t>
+          <t>43517; 70790</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91253; 141103</t>
+          <t>110562; 164756</t>
         </is>
       </c>
     </row>
